--- a/assets/constructions/examples/ctd_eths_roundholder.xlsx
+++ b/assets/constructions/examples/ctd_eths_roundholder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E2-30-16</t>
+          <t>E2-30-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -610,12 +630,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ISO_5609:16</t>
+          <t>ISO_5609:10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LIK_E2-16</t>
+          <t>LIK_E2-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -624,7 +644,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -677,16 +697,22 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E2-30-25</t>
+          <t>19.3025DRX60</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -713,12 +739,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LIK_E2-25</t>
+          <t>EWS_HA-25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -730,26 +756,28 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>68</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
+        <v>70</v>
+      </c>
+      <c r="S3" t="n">
+        <v>70</v>
+      </c>
+      <c r="T3" t="n">
+        <v>110</v>
+      </c>
+      <c r="U3" t="n">
         <v>60</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
@@ -758,7 +786,7 @@
         </is>
       </c>
       <c r="Y3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -772,23 +800,37 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
-        </is>
-      </c>
+          <t>2021/ http://www.tool-cloud.de/zh/online-catalogue</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E2-30-10</t>
+          <t>VDI-E1-30x16x66</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>KFH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VDI HOLDERS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DIN 69880</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>DIN_69880_1:VDI30</t>
@@ -806,21 +848,21 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ISO_5609:10</t>
+          <t>ISO_9766:16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LIK_E2-10</t>
+          <t>ISO_9766:D16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -828,12 +870,14 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>36</v>
+      </c>
       <c r="P4" t="n">
         <v>68</v>
       </c>
@@ -841,43 +885,45 @@
         <v>30</v>
       </c>
       <c r="R4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>68</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>BLIND</t>
         </is>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
-        </is>
-      </c>
+          <t>2020 / KFH Website</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E2-30-20</t>
+          <t>E2-30-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -904,12 +950,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LIK_E2-20</t>
+          <t>LIK_E2-08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -918,7 +964,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -971,11 +1017,17 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E2-30-32</t>
+          <t>E2-30-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1002,12 +1054,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LIK_E2-32</t>
+          <t>LIK_E2-12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1016,7 +1068,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1037,7 +1089,7 @@
         <v>30</v>
       </c>
       <c r="R6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
@@ -1069,6 +1121,12 @@
           <t>2018/!Likon_Инструментальный каталог_2018.pdf</t>
         </is>
       </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
